--- a/OTC_BOOK.xlsx
+++ b/OTC_BOOK.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-0</v>
@@ -915,7 +915,7 @@
         <v>38.2</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-0.5</v>
@@ -989,7 +989,7 @@
         <v>1.4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>1.5</v>
@@ -1026,7 +1026,7 @@
         <v>5.6</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>-3.5</v>
@@ -1099,8 +1099,10 @@
       <c r="E14" s="13" t="n">
         <v>11.8</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <v>0.01</v>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G14" s="9" t="n">
         <v>0.1</v>
@@ -1247,8 +1249,10 @@
       <c r="E18" s="13" t="n">
         <v>3.8</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <v>0.07000000000000001</v>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="9" t="n">
         <v>-2</v>
@@ -1284,8 +1288,10 @@
       <c r="E19" s="12" t="n">
         <v>3.4</v>
       </c>
-      <c r="F19" s="6" t="n">
-        <v>0.06</v>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G19" s="6" t="n">
         <v>0.2</v>
@@ -1357,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1444,117 +1450,117 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IONI</t>
+          <t>SNTX</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>I-ON Digital Corp.</t>
+          <t>Suntex Enterprises, Inc.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-28</v>
+        <v>37</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>SMAL</t>
+          <t>STLY</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Summit Bancshares, Inc.</t>
+          <t>HG Holdings, Inc.</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G6" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I6" s="9" t="n">
         <v>28</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ADKT</t>
+          <t>IONI</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>The Adirondack Trust Compa</t>
+          <t>I-ON Digital Corp.</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>BKUTK</t>
+          <t>SMAL</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Bank of Utica</t>
+          <t>Summit Bancshares, Inc.</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1563,33 +1569,33 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>171.8</v>
+        <v>14.5</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>BKUT</t>
+          <t>ADKT</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Bank of Utica</t>
+          <t>The Adirondack Trust Compa</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1598,92 +1604,92 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.48</v>
+        <v>0.26</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>34.2</v>
+        <v>52</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>STLY</t>
+          <t>BKUTK</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>HG Holdings, Inc.</t>
+          <t>Bank of Utica</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>10.3</v>
+        <v>171.8</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SNTX</t>
+          <t>BKUT</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Suntex Enterprises, Inc.</t>
+          <t>Bank of Utica</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>5.1</v>
+        <v>34.2</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1703,7 +1709,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>3.5</v>
@@ -1724,152 +1730,152 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>IGPK</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Integrated Cannabis Soluti</t>
+          <t>Asia Broadband, Inc.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>WNMLA</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Asia Broadband, Inc.</t>
+          <t>Winmill &amp; Co. Incorporated</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>16.7</v>
+        <v>2.9</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>47.9</v>
+        <v>7.7</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>WNMLA</t>
+          <t>HHSE</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Winmill &amp; Co. Incorporated</t>
+          <t>Hannover House, Inc.</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.9</v>
+        <v>28.7</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>7.7</v>
+        <v>10.6</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>HHSE</t>
+          <t>VXRT</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Hannover House, Inc.</t>
+          <t>Vaxart, Inc.</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.3</v>
+        <v>1.43</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>28.7</v>
+        <v>3.2</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>10.6</v>
+        <v>117.4</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VXRT</t>
+          <t>WSTL</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vaxart, Inc.</t>
+          <t>Westell Technologies, Inc.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1878,68 +1884,70 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="F17" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G17" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>29</v>
-      </c>
       <c r="H17" s="12" t="n">
-        <v>117.4</v>
+        <v>62.1</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>WSTL</t>
+          <t>ECRO</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Westell Technologies, Inc.</t>
+          <t>ECC Capital Corporation</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.96</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>62.1</v>
+        <v>18.5</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ECRO</t>
+          <t>MRTI</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ECC Capital Corporation</t>
+          <t>Maxus Realty Trust, Inc.</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1948,33 +1956,33 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.15</v>
+        <v>0.64</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>18.5</v>
+        <v>89.2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>MRTI</t>
+          <t>PYYX</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Maxus Realty Trust, Inc.</t>
+          <t>Pyxus International, Inc.</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1983,22 +1991,22 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>38</v>
+        <v>-120</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>89.2</v>
+        <v>77.3</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -2018,7 +2026,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>5.3</v>
@@ -2039,36 +2047,36 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>PYYX</t>
+          <t>FPBC</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Pyxus International, Inc.</t>
+          <t>First Pacific Bancorp</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>3.6</v>
+        <v>21.9</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>77.3</v>
+        <v>16</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -2088,7 +2096,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>5.6</v>
@@ -2123,7 +2131,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>5.2</v>
@@ -2158,7 +2166,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>5.7</v>
@@ -2193,7 +2201,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>3.1</v>
@@ -2228,7 +2236,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>6.9</v>
@@ -2298,7 +2306,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>3.4</v>
@@ -2438,7 +2446,7 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>5.3</v>
@@ -2473,7 +2481,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.54</v>
+        <v>3.31</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>4.9</v>
@@ -2508,7 +2516,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>3.6</v>
@@ -2564,222 +2572,222 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>BSRTF</t>
+          <t>DYNR</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>BSR Real Estate Investment</t>
+          <t>DynaResource, Inc.</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.53</v>
+        <v>2.24</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20.1</v>
+        <v>4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>5</v>
+        <v>-16</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>385.1</v>
+        <v>22.6</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>DYNR</t>
+          <t>CBBI</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>DynaResource, Inc.</t>
+          <t>CBB Bancorp, Inc.</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.26</v>
+        <v>0.54</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>22.6</v>
+        <v>149.4</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>38</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>CBBI</t>
+          <t>JFWV</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>CBB Bancorp, Inc.</t>
+          <t>JSB Financial Inc.</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.54</v>
+        <v>0.91</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>149.4</v>
+        <v>33.5</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>JFWV</t>
+          <t>KCLI</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>JSB Financial Inc.</t>
+          <t>Kansas City Life Insurance</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.91</v>
+        <v>0.52</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>6.1</v>
+        <v>15.3</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>33.5</v>
+        <v>350.2</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>KCLI</t>
+          <t>ETST</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Kansas City Life Insurance</t>
+          <t>Earth Science Tech, Inc.</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.52</v>
+        <v>3.45</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>15.3</v>
+        <v>6.9</v>
       </c>
       <c r="F41" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G41" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G41" s="6" t="n">
-        <v>-34</v>
-      </c>
       <c r="H41" s="12" t="n">
-        <v>350.2</v>
+        <v>25.4</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>IDWM</t>
+          <t>MKIN</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>IDW Media Holdings, Inc.</t>
+          <t>MCNB Banks, Inc.</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>21.2</v>
+        <v>10.3</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>1159.6</v>
+        <v>22.9</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>ETST</t>
+          <t>UTGN</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Earth Science Tech, Inc.</t>
+          <t>UTG, Inc.</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -2788,33 +2796,33 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>3.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>6.9</v>
+        <v>5.1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>25.4</v>
+        <v>182.1</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>MKIN</t>
+          <t>AMEN</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>MCNB Banks, Inc.</t>
+          <t>AMEN Properties, Inc.</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2823,33 +2831,33 @@
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.55</v>
+        <v>3.77</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>10.3</v>
+        <v>6.9</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>22.9</v>
+        <v>27.7</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>UTGN</t>
+          <t>DTRL</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>UTG, Inc.</t>
+          <t>The Detroit Legal News Com</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -2858,68 +2866,68 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>182.1</v>
+        <v>11.3</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>AMEN</t>
+          <t>RSRV</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>AMEN Properties, Inc.</t>
+          <t>The Reserve Petroleum Comp</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>27.7</v>
+        <v>32.3</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>DTRL</t>
+          <t>CHKR</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>The Detroit Legal News Com</t>
+          <t>Chesapeake Granite Wash Tr</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -2928,80 +2936,80 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.95</v>
+        <v>1.84</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>11.3</v>
+        <v>17.8</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>RSRV</t>
+          <t>TXRP</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>The Reserve Petroleum Comp</t>
+          <t>TX Rail Products, Inc</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.92</v>
+        <v>3.34</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>32.3</v>
+        <v>9.1</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>CHKR</t>
+          <t>CIZN</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Chesapeake Granite Wash Tr</t>
+          <t>Citizens Holding Company</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1.84</v>
+        <v>0.84</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>16</v>
@@ -3010,68 +3018,68 @@
         <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>17.8</v>
+        <v>58.2</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>TXRP</t>
+          <t>ITFS</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>TX Rail Products, Inc</t>
+          <t>Itafos Inc.</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>3.34</v>
+        <v>0.75</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>16</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>9.1</v>
+        <v>325.3</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>CIZN</t>
+          <t>CIBN</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Citizens Holding Company</t>
+          <t>Community Investors Bancor</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>16</v>
@@ -3080,199 +3088,131 @@
         <v>0</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>58.2</v>
+        <v>21.8</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>ITFS</t>
+          <t>FNFI</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Itafos Inc.</t>
+          <t>First Niles Financial, Inc</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>6.1</v>
+        <v>11.7</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>325.3</v>
+        <v>9.9</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>CIBN</t>
+          <t>XERI</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Community Investors Bancor</t>
+          <t>Xeriant, Inc.</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>0.9399999999999999</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>21.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>FNFI</t>
+          <t>USAQ</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>First Niles Financial, Inc</t>
+          <t>QHSLab, Inc.</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.57</v>
+        <v>3.09</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>11.7</v>
+        <v>6.8</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>9.9</v>
+        <v>4.8</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>XERI</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Xeriant, Inc.</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="H55" s="12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I55" s="6" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>USAQ</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>QHSLab, Inc.</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F56" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H56" s="13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>52 names pass. Low P/B in OTC often means impaired assets or a controlled company — pair with the Net-Nets and Cash Shells tabs.</t>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>50 names pass. Low P/B in OTC often means impaired assets or a controlled company — pair with the Net-Nets and Cash Shells tabs.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A58:I58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3783,19 +3723,19 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>SNTI</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>LGL GROUP INC</t>
+          <t>Senti Biosciences, Inc.</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -3803,29 +3743,29 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>40.4</v>
+        <v>11</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1</v>
+        <v>-3.21</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>SNTI</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Senti Biosciences, Inc.</t>
+          <t>LGL GROUP INC</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -3840,112 +3780,114 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11</v>
+        <v>40.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-3.21</v>
+        <v>0.91</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-22</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>GLP</t>
+          <t>CSCIF</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>GLOBAL PARTNERS LP</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>COSCIENS Biopharma Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1676.5</v>
+        <v>1.9</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>30</v>
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>CASIF</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>CASI Pharmaceuticals, Inc.</t>
+          <t>SWK Holdings Corp</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2.7</v>
+        <v>191</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>45</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>MVST</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cryoport, Inc.</t>
+          <t>Microvast Holdings, Inc.</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3953,73 +3895,77 @@
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>870.4</v>
+        <v>244.2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1.78</v>
+        <v>0.45</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>MPTI</t>
+          <t>PAIYY</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>M-tron Industries, Inc.</t>
+          <t>Aesthetic Medical Internat</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>263.6</v>
+        <v>0.3</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>6</v>
+        <v>-0.09</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>LIDR</t>
+          <t>CTHH</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>AEye, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>25</v>
+          <t>QWEST CORP</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>15/25</t>
+        </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -4027,36 +3973,40 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>2</v>
+        <v>256.8</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>HLLY</t>
+          <t>MPTI</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Holley Inc.</t>
+          <t>M-tron Industries, Inc.</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -4064,36 +4014,36 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>301.5</v>
+        <v>263.6</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.66</v>
+        <v>2.22</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MVST</t>
+          <t>HTOO</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Microvast Holdings, Inc.</t>
+          <t>Fusion Fuel Green PLC</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -4101,29 +4051,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>244.2</v>
+        <v>14.7</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>53</v>
+        <v>2.68</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>JFB</t>
+          <t>GLP</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>JFB Construction Holdings</t>
+          <t>GLOBAL PARTNERS LP</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -4132,7 +4084,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -4140,40 +4092,36 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1676.5</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>30</v>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>LMMY</t>
+          <t>CASIF</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Exousia Bio, Inc.</t>
+          <t>CASI Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4181,38 +4129,36 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-0.05</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>45</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>CWLXF</t>
+          <t>QVCG</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>C21 Investments Inc.</t>
+          <t>QVC Group, Inc.</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -4220,7 +4166,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0</v>
+        <v>769.7</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -4234,26 +4180,26 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NBND</t>
+          <t>WVE</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>NetBrands Corp.</t>
+          <t>Wave Life Sciences, Inc.</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4261,40 +4207,36 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>785.8</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>QVCG</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>QVC Group, Inc.</t>
+          <t>Cryoport, Inc.</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -4302,51 +4244,47 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>769.7</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>870.4</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>DWAY</t>
+          <t>BBUC</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Driveitaway Holdings, Inc.</t>
+          <t>Brookfield Business Corp</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>2.2</v>
+        <v>5229.5</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.27</v>
+        <v>0.96</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -4355,67 +4293,63 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>PAIYY</t>
+          <t>OPAD</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Aesthetic Medical Internat</t>
+          <t>Offerpad Solutions Inc.</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3</v>
+        <v>16.5</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.44</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>14</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>APOS</t>
+          <t>PTN</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Apollo Global Management,</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>PALATIN TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -4423,38 +4357,36 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>74609.60000000001</v>
+        <v>18</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.69</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>PNXP</t>
+          <t>CULP</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>PINEAPPLE EXPRESS CANNABIS</t>
+          <t>CULP INC</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -4462,12 +4394,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>45.3</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
@@ -4476,26 +4406,26 @@
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>WVE</t>
+          <t>HVIIR</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Wave Life Sciences, Inc.</t>
+          <t>ONE Nuclear Energy Inc.</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -4503,77 +4433,75 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>785.8</v>
+        <v>232.7</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>16</v>
+        <v>1.23</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>MSBB</t>
+          <t>LIDR</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Mercer Bancorp, Inc.</t>
+          <t>AEye, Inc.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>21.2</v>
+        <v>55.3</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>STRS</t>
+          <t>MNTS</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>STRATUS PROPERTIES INC</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>Momentus Inc.</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -4581,53 +4509,47 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.5</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>PLTYF</t>
+          <t>RVPH</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Plastec Technologies, Ltd.</t>
+          <t>REVIVA PHARMACEUTICALS HOL</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.1</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>0.35</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
@@ -4636,28 +4558,26 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>SNBRQ</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corp</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>HENNESSY ADVISORS INC</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -4665,12 +4585,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>82.2</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -4679,37 +4597,37 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>MYCB</t>
+          <t>MYPS</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>My City Builders, Inc.</t>
+          <t>PLAYSTUDIOS, Inc.</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>2.2</v>
+        <v>59.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>-72.2</v>
+        <v>0.29</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
@@ -4718,28 +4636,26 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>GTES</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Gates Industrial Corp Ltd.</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>Quantum-Si Inc</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -4747,10 +4663,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>6718.3</v>
+        <v>151.4</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1.9</v>
+        <v>0.84</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -4759,58 +4675,56 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>RBOT</t>
+          <t>OPFI</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Vicarious Surgical Inc.</t>
+          <t>OppFi Inc.</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.3</v>
+        <v>537.1</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>61</v>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>DREM</t>
+          <t>LMMY</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Dream Homes &amp; Development</t>
+          <t>Exousia Bio, Inc.</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -4825,10 +4739,12 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>-1.78</v>
+        <v>0.1</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -4837,19 +4753,19 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>SIGY</t>
+          <t>CWLXF</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Sigyn Therapeutics, Inc.</t>
+          <t>C21 Investments Inc.</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
@@ -4860,14 +4776,16 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
@@ -4876,19 +4794,19 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>CLNV</t>
+          <t>NBND</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Clean Vision Corp</t>
+          <t>NetBrands Corp.</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -4899,14 +4817,16 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>-0.36</v>
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -4915,19 +4835,19 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>CSCIF</t>
+          <t>DWAY</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>COSCIENS Biopharma Inc.</t>
+          <t>Driveitaway Holdings, Inc.</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
@@ -4942,10 +4862,12 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
@@ -4954,19 +4876,19 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>WYTC</t>
+          <t>PNXP</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>WYTEC INTERNATIONAL INC</t>
+          <t>PINEAPPLE EXPRESS CANNABIS</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
@@ -4977,14 +4899,16 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -4993,39 +4917,37 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>FTAIM</t>
+          <t>MSBB</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>FTAI Aviation Ltd.</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>Mercer Bancorp, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>8</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>21174.5</v>
+        <v>21.2</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>47.93</v>
+        <v>0.84</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -5034,37 +4956,41 @@
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>BASA</t>
+          <t>STRS</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>BASANITE, INC.</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>15</v>
+          <t>STRATUS PROPERTIES INC</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>15/25</t>
+        </is>
       </c>
       <c r="D37" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>-0.67</v>
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -5073,25 +4999,23 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>CTHH</t>
+          <t>PLTYF</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>QWEST CORP</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>Plastec Technologies, Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>8</v>
@@ -5102,7 +5026,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>256.8</v>
+        <v>0</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
@@ -5116,37 +5040,41 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ECIA</t>
+          <t>SNBRQ</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>ENCISION INC</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>15</v>
+          <t>Sleep Number Corp</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>15/25</t>
+        </is>
       </c>
       <c r="D39" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -5155,19 +5083,19 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>ABIT</t>
+          <t>MYCB</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Athena Bitcoin Global</t>
+          <t>My City Builders, Inc.</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
@@ -5182,10 +5110,12 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>0.03</v>
+        <v>2.2</v>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
@@ -5194,37 +5124,39 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>BPTH</t>
+          <t>GTES</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>BIO-PATH HOLDINGS, INC.</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>15</v>
+          <t>Gates Industrial Corp Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>15/25</t>
+        </is>
       </c>
       <c r="D41" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0</v>
+        <v>6718.3</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0</v>
+        <v>1.91</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -5233,19 +5165,19 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>YGMZF</t>
+          <t>RBOT</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>MingZhu Logistics Holdings</t>
+          <t>Vicarious Surgical Inc.</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
@@ -5260,10 +5192,12 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
@@ -5272,19 +5206,19 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>LDSN</t>
+          <t>DREM</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Aphoenity International Ho</t>
+          <t>Dream Homes &amp; Development</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -5299,10 +5233,12 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>-23.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -5311,19 +5247,19 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>SIGY</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>SWK Holdings Corp</t>
+          <t>Sigyn Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
@@ -5334,14 +5270,16 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>191</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>0.82</v>
+        <v>0.1</v>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -5350,19 +5288,19 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>AHRO</t>
+          <t>CLNV</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Authentic Holdings, Inc.</t>
+          <t>Clean Vision Corp</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -5377,10 +5315,12 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>0.32</v>
+        <v>5.8</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -5389,19 +5329,19 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>BBUC</t>
+          <t>WYTC</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Brookfield Business Corp</t>
+          <t>WYTEC INTERNATIONAL INC</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
@@ -5412,14 +5352,16 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>5229.5</v>
-      </c>
-      <c r="G46" s="9" t="n">
-        <v>0.98</v>
+        <v>16.6</v>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
@@ -5428,19 +5370,19 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ZIVO</t>
+          <t>BASA</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Zivo Bioscience, Inc.</t>
+          <t>BASANITE, INC.</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
@@ -5455,10 +5397,12 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>-4.42</v>
+        <v>7.4</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -5467,19 +5411,19 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>BLMH</t>
+          <t>WCHD</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>BLUM HOLDINGS, INC.</t>
+          <t>WeCapital Holdings, Inc.</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
@@ -5490,14 +5434,16 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G48" s="9" t="n">
-        <v>-0.63</v>
+        <v>0</v>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -5506,19 +5452,19 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>CELG-RI</t>
+          <t>ECIA</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB CO</t>
+          <t>ENCISION INC</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
@@ -5529,16 +5475,14 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0.27</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -5547,19 +5491,19 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>RMTHF</t>
+          <t>ABIT</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>MAGIC SOFTWARE ENTERPRISES</t>
+          <t>Athena Bitcoin Global</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
@@ -5570,11 +5514,11 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
@@ -5588,25 +5532,23 @@
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ANEB</t>
+          <t>BPTH</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Anebulo Pharmaceuticals, I</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>15/25</t>
-        </is>
+          <t>BIO-PATH HOLDINGS, INC.</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>8</v>
@@ -5617,10 +5559,12 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>1.55</v>
+        <v>0</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -5629,19 +5573,19 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>CYTOF</t>
+          <t>YGMZF</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Altamira Therapeutics Ltd.</t>
+          <t>MingZhu Logistics Holdings</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
@@ -5652,7 +5596,7 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
@@ -5670,19 +5614,19 @@
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>STQN</t>
+          <t>LDSN</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC ACQUISITIONS INC</t>
+          <t>Aphoenity International Ho</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
@@ -5697,10 +5641,12 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>-954.53</v>
+        <v>2.2</v>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -5709,19 +5655,19 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>CYAN</t>
+          <t>AHRO</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>CYANOTECH CORP</t>
+          <t>Authentic Holdings, Inc.</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
@@ -5736,10 +5682,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
@@ -5748,19 +5694,19 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>RDGA</t>
+          <t>ZIVO</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>RIDGEFIELD ACQUISITION COR</t>
+          <t>Zivo Bioscience, Inc.</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
@@ -5771,11 +5717,11 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
@@ -5789,19 +5735,19 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>HTOO</t>
+          <t>BLMH</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Fusion Fuel Green PLC</t>
+          <t>BLUM HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
@@ -5812,14 +5758,16 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
@@ -5828,19 +5776,19 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>CELG-RI</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>iRhythm Holdings, Inc.</t>
+          <t>BRISTOL MYERS SQUIBB CO</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
@@ -5855,29 +5803,33 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>3769.6</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>INDV</t>
+          <t>RMTHF</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Indivior Pharmaceuticals,</t>
+          <t>MAGIC SOFTWARE ENTERPRISES</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
@@ -5892,49 +5844,53 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>4527.9</v>
-      </c>
-      <c r="G58" s="9" t="n">
-        <v>-21.73</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>MIBE</t>
+          <t>ANEB</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>MIAMI BREEZE CAR CARE INC</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>15</v>
+          <t>Anebulo Pharmaceuticals, I</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>15/25</t>
+        </is>
       </c>
       <c r="D59" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.2</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>1.54</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -5943,19 +5899,19 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>CYTOF</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>ENERGY CO OF PARANA</t>
+          <t>Altamira Therapeutics Ltd.</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
@@ -5970,10 +5926,12 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>2287.5</v>
-      </c>
-      <c r="G60" s="9" t="n">
-        <v>1.95</v>
+        <v>0</v>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
@@ -5982,97 +5940,103 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>OPAD</t>
+          <t>STQN</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Offerpad Solutions Inc.</t>
+          <t>STRATEGIC ACQUISITIONS INC</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H61" s="15" t="n">
-        <v>14</v>
+        <v>18.3</v>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-02-23</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>PTN</t>
+          <t>CYAN</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>PALATIN TECHNOLOGIES INC</t>
+          <t>CYANOTECH CORP</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D62" s="9" t="n">
         <v>8</v>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H62" s="16" t="n">
-        <v>1</v>
+        <v>0.46</v>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-13</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>LPSN</t>
+          <t>RDGA</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>LIVEPERSON INC</t>
+          <t>RIDGEFIELD ACQUISITION COR</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D63" s="6" t="n">
         <v>8</v>
@@ -6083,33 +6047,37 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="H63" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>HUMA</t>
+          <t>IRTC</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Humacyte, Inc.</t>
+          <t>iRhythm Holdings, Inc.</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D64" s="9" t="n">
         <v>8</v>
@@ -6120,24 +6088,24 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>94.90000000000001</v>
+        <v>3769.6</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>4.22</v>
+        <v>20.27</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>161 names (Form 15 = true deregistration, scores highest; Form 25 alone is often a routine security delisting). High insider % + going dark = the squeeze-out setup.</t>
+          <t>164 names (Form 15 = true deregistration, scores highest; Form 25 alone is often a routine security delisting). High insider % + going dark = the squeeze-out setup.</t>
         </is>
       </c>
     </row>
@@ -6237,12 +6205,12 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>PMCB</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>CarParts.com, Inc.</t>
+          <t>PharmaCyte Biotech, Inc.</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
@@ -6254,7 +6222,7 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>51.3</v>
+        <v>4.6</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -6268,19 +6236,19 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-11-18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>PMCB</t>
+          <t>ARTL</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>PharmaCyte Biotech, Inc.</t>
+          <t>ARTELO BIOSCIENCES, INC.</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -6292,7 +6260,7 @@
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -6306,19 +6274,19 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-07-11</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>FUBO</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>fuboTV Inc. /FL</t>
+          <t>Neuphoria Therapeutics Inc.</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -6330,7 +6298,7 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>271.4</v>
+        <v>20</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -6344,19 +6312,19 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>DCOY</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeutics Inc.</t>
+          <t>Salarius Pharmaceuticals, In</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -6368,7 +6336,7 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>23.3</v>
+        <v>2.2</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -6382,7 +6350,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6374,7 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>62.6</v>
+        <v>53.6</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -6427,12 +6395,12 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>QNCX</t>
+          <t>SRXH</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Quince Therapeutics, Inc.</t>
+          <t>SRX Global Inc.</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -6444,7 +6412,7 @@
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -6458,23 +6426,23 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>DOMO</t>
+          <t>ONCO</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>DOMO, INC.</t>
+          <t>Onconetix, Inc.</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -6482,7 +6450,7 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>109.3</v>
+        <v>2.4</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -6491,28 +6459,28 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>HRTX</t>
+          <t>RNAZ</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>HERON THERAPEUTICS, INC. /DE</t>
+          <t>Transcode Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -6520,7 +6488,7 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>79</v>
+        <v>2.1</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -6529,28 +6497,28 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>LPSN</t>
+          <t>APUS</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LIVEPERSON INC</t>
+          <t>Apimeds Pharmaceuticals US,</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -6558,7 +6526,7 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>24.5</v>
+        <v>2.9</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -6567,28 +6535,28 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-12-02</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>PRPL</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Purple Innovation, Inc.</t>
+          <t>SmartKem, Inc.</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -6596,7 +6564,7 @@
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>46.5</v>
+        <v>0.9</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -6605,28 +6573,28 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>NCRA</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>ACCENDRA HEALTH INC/VA/</t>
+          <t>NOCERA, INC.</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -6634,7 +6602,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>247.4</v>
+        <v>3.1</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -6643,28 +6611,28 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-11-03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>CHRS</t>
+          <t>TRNR</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Coherus Oncology, Inc.</t>
+          <t>Interactive Strength, Inc.</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
@@ -6672,7 +6640,7 @@
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>215.9</v>
+        <v>1.5</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -6681,28 +6649,28 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-06-11</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SKYE</t>
+          <t>IPW</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Skye Bioscience, Inc.</t>
+          <t>iPower Inc.</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -6710,7 +6678,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -6719,28 +6687,28 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-12-23</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>UIS</t>
+          <t>AEMD</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>UNISYS CORP</t>
+          <t>AETHLON MEDICAL INC</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -6748,7 +6716,7 @@
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>258.1</v>
+        <v>3.4</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -6757,66 +6725,66 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>CMLSQ</t>
+          <t>JAGX</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>CUMULUS MEDIA INC</t>
+          <t>Jaguar Health, Inc.</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-10-01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>COSM</t>
+          <t>WWR</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Cosmos Health Inc.</t>
+          <t>WESTWATER RESOURCES, INC.</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -6824,11 +6792,11 @@
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>13.2</v>
+        <v>70.3</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -6838,23 +6806,23 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Verb Technology Company, Inc</t>
+          <t>CarParts.com, Inc.</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -6862,37 +6830,37 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>212.6</v>
+        <v>67.2</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>COHN</t>
+          <t>HRTX</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cohen &amp; Co Inc.</t>
+          <t>HERON THERAPEUTICS, INC. /DE</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -6900,37 +6868,37 @@
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>29.9</v>
+        <v>55.6</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>PRPL</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>WW INTERNATIONAL, INC.</t>
+          <t>Purple Innovation, Inc.</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -6938,37 +6906,37 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>192</v>
+        <v>11.4</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>OPTT</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Ocean Power Technologies, In</t>
+          <t>ACCENDRA HEALTH INC/VA/</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -6976,11 +6944,11 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>74.59999999999999</v>
+        <v>60.9</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -6990,23 +6958,23 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>SANDRIDGE ENERGY INC</t>
+          <t>Werewolf Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -7014,37 +6982,37 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>517.6</v>
+        <v>47.6</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>DHX</t>
+          <t>HIND</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>DHI GROUP, INC.</t>
+          <t>Vyome Holdings, Inc</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
@@ -7052,11 +7020,11 @@
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>164.2</v>
+        <v>14.4</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -7066,23 +7034,23 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>BEAZER HOMES USA INC</t>
+          <t>PDS Biotechnology Corp</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -7090,37 +7058,37 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>739.4</v>
+        <v>47.2</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-05-02</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>CHRS</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Comstock Holding Companies,</t>
+          <t>Coherus Oncology, Inc.</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -7128,11 +7096,11 @@
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>153.9</v>
+        <v>192.4</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -7142,23 +7110,23 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>RYM</t>
+          <t>PTHS</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>RYTHM, Inc.</t>
+          <t>Channel Therapeutics Corp</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -7166,11 +7134,11 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>60.1</v>
+        <v>83.8</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -7180,23 +7148,23 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-04-17</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>NextCure, Inc.</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -7204,11 +7172,11 @@
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>32.2</v>
+        <v>17.3</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -7218,23 +7186,23 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>PASG</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>GoPro, Inc.</t>
+          <t>Passage BIO, Inc.</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -7242,11 +7210,11 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>136.7</v>
+        <v>16.1</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -7256,23 +7224,23 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>XTIA</t>
+          <t>QNCX</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>XTI Aerospace, Inc.</t>
+          <t>Quince Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -7280,11 +7248,11 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>71.2</v>
+        <v>8.4</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -7294,23 +7262,23 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>FTCI</t>
+          <t>SKYE</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>FTC Solar, Inc.</t>
+          <t>Skye Bioscience, Inc.</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -7318,11 +7286,11 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>82.3</v>
+        <v>7.4</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -7332,23 +7300,23 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>OTLK</t>
+          <t>UIS</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Outlook Therapeutics, Inc.</t>
+          <t>UNISYS CORP</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
@@ -7356,11 +7324,11 @@
         </is>
       </c>
       <c r="E34" s="13" t="n">
-        <v>234.8</v>
+        <v>173.9</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -7370,35 +7338,35 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>USGO</t>
+          <t>CMLSQ</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>U.S. GoldMining Inc.</t>
+          <t>CUMULUS MEDIA INC</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>112.8</v>
+        <v>0.1</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -7408,23 +7376,23 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>USAR</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>USA Rare Earth, Inc.</t>
+          <t>REGIS CORP</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -7432,37 +7400,37 @@
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>4973.9</v>
+        <v>70</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>STRRP</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Angel Studios, Inc.</t>
+          <t>Hudson Global, Inc.</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -7470,7 +7438,7 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>596.5</v>
+        <v>40</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -7479,28 +7447,28 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Z Squared Inc.</t>
+          <t>Maison Solutions Inc.</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -7508,7 +7476,7 @@
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>531.3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -7517,66 +7485,66 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>VREOF</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Vireo Growth Inc.</t>
+          <t>Allbirds, Inc.</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>773.5</v>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>WAY</t>
+          <t>OLOX</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Waystar Holding Corp.</t>
+          <t>SAFE &amp; GREEN HOLDINGS CORP.</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
@@ -7584,7 +7552,7 @@
         </is>
       </c>
       <c r="E40" s="13" t="n">
-        <v>3542.8</v>
+        <v>0.5</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -7598,23 +7566,23 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-12-02</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>OCGN</t>
+          <t>AMZE</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Ocugen, Inc.</t>
+          <t>AMAZE HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -7622,7 +7590,7 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>419.8</v>
+        <v>1</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -7631,28 +7599,28 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-04-16</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>PPCB</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Diversified Energy Co</t>
+          <t>Propanc Biopharma, Inc.</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
@@ -7660,7 +7628,7 @@
         </is>
       </c>
       <c r="E42" s="13" t="n">
-        <v>940.2</v>
+        <v>1.4</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -7669,28 +7637,28 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CLVT</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>CLARIVATE PLC</t>
+          <t>Verb Technology Company, Inc</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -7698,7 +7666,7 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>1304</v>
+        <v>231.2</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -7712,23 +7680,23 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-04-25</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>LXU</t>
+          <t>VENU</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>LSB INDUSTRIES, INC.</t>
+          <t>Venu Holding Corp</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
@@ -7736,7 +7704,7 @@
         </is>
       </c>
       <c r="E44" s="13" t="n">
-        <v>818.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -7745,28 +7713,28 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>COHN</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP /MI/</t>
+          <t>Cohen &amp; Co Inc.</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
@@ -7774,7 +7742,7 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>707</v>
+        <v>32.3</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -7783,28 +7751,28 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>CHTRP</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>REGIS CORP</t>
+          <t>CHARTER COMMUNICATIONS, INC.</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
@@ -7812,7 +7780,7 @@
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -7821,28 +7789,28 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TTI</t>
+          <t>NCMI</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>TETRA TECHNOLOGIES INC</t>
+          <t>National CineMedia, Inc.</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -7850,7 +7818,7 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>1513.7</v>
+        <v>202.6</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -7859,28 +7827,28 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>VISK</t>
+          <t>NINE</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Viskase Holdings, Inc.</t>
+          <t>Nine Energy Service, Inc.</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -7888,7 +7856,7 @@
         </is>
       </c>
       <c r="E48" s="13" t="n">
-        <v>0</v>
+        <v>127.4</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -7897,78 +7865,78 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>LOGC</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ContextLogic Holdings Inc.</t>
+          <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>154.1</v>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-05-07</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>VREOF</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Great Elm Group, Inc.</t>
+          <t>Vireo Growth Inc.</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
-        <v>0</v>
+        <v>453.7</v>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -7978,23 +7946,23 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ASUR</t>
+          <t>OPTT</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>ASURE SOFTWARE INC</t>
+          <t>Ocean Power Technologies, In</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
@@ -8002,7 +7970,7 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -8016,23 +7984,23 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>CENTRUS ENERGY CORP</t>
+          <t>SANDRIDGE ENERGY INC</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -8040,7 +8008,7 @@
         </is>
       </c>
       <c r="E52" s="13" t="n">
-        <v>3765.2</v>
+        <v>523.9</v>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
@@ -8049,36 +8017,36 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>BMNM</t>
+          <t>DOMO</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>BIMINI CAPITAL MANAGEMENT, I</t>
+          <t>DOMO, INC.</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0</v>
+        <v>153.9</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -8092,23 +8060,23 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>APTN</t>
+          <t>DHX</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>ADAPTIN BIO, INC.</t>
+          <t>DHI GROUP, INC.</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -8116,7 +8084,7 @@
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>0</v>
+        <v>199.1</v>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
@@ -8130,23 +8098,23 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ARTL</t>
+          <t>ASUR</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>ARTELO BIOSCIENCES, INC.</t>
+          <t>ASURE SOFTWARE INC</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
@@ -8154,7 +8122,7 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0</v>
+        <v>232.8</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -8168,31 +8136,31 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-04-16</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>BMNM</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>WARRIOR MET COAL, INC.</t>
+          <t>BIMINI CAPITAL MANAGEMENT, I</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>4782.8</v>
+        <v>33.5</v>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
@@ -8206,23 +8174,23 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-12-10</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>STRRP</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Hudson Global, Inc.</t>
+          <t>BEAZER HOMES USA INC</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
@@ -8230,7 +8198,7 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0</v>
+        <v>911.7</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
@@ -8239,28 +8207,28 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-11-13</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>ALMS</t>
+          <t>OBX</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>ALUMIS INC.</t>
+          <t>Obsidian Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
@@ -8268,7 +8236,7 @@
         </is>
       </c>
       <c r="E58" s="13" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
@@ -8282,23 +8250,23 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>RYM</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Werewolf Therapeutics, Inc.</t>
+          <t>RYTHM, Inc.</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
@@ -8306,7 +8274,7 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0</v>
+        <v>49.6</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
@@ -8320,23 +8288,23 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-10-08</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>HIND</t>
+          <t>SRFM</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Vyome Holdings, Inc</t>
+          <t>SURF AIR MOBILITY INC.</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
@@ -8344,7 +8312,7 @@
         </is>
       </c>
       <c r="E60" s="13" t="n">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
@@ -8358,23 +8326,23 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>DCOY</t>
+          <t>CJMB</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Salarius Pharmaceuticals, In</t>
+          <t>CALLAN JMB INC.</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
@@ -8382,7 +8350,7 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
@@ -8396,23 +8364,23 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>OBX</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Obsidian Therapeutics, Inc.</t>
+          <t>Z Squared Inc.</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
@@ -8420,7 +8388,7 @@
         </is>
       </c>
       <c r="E62" s="13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
@@ -8434,23 +8402,23 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>SRFM</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>SURF AIR MOBILITY INC.</t>
+          <t>Cosmos Health Inc.</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
@@ -8458,7 +8426,7 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -8472,23 +8440,23 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>LRHC</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>PDS Biotechnology Corp</t>
+          <t>La Rosa Holdings Corp.</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
@@ -8496,7 +8464,7 @@
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
@@ -8510,14 +8478,14 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-11-13</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>143 names with an NOL rights plan in the last ~18 months. Best shells: micro-cap + cash-rich + NOL ≫ market cap.</t>
+          <t>145 names with an NOL rights plan in the last ~18 months. Best shells: micro-cap + cash-rich + NOL ≫ market cap.</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8709,7 @@
         <v>2.1</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>46</v>
@@ -9285,7 +9253,7 @@
         <v>4.5</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>32</v>
@@ -9557,7 +9525,7 @@
         <v>3.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>30</v>
@@ -9637,41 +9605,41 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>SRBIF</t>
+          <t>VONOY</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Serabi Gold plc</t>
+          <t>Vonovia SE</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1.18</v>
+        <v>0.54</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>250</v>
+        <v>16697</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>VONOY</t>
+          <t>VNNVF</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -9699,57 +9667,57 @@
         <v>26</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>16697</v>
+        <v>16841</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>VNNVF</t>
+          <t>ALGGY</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Vonovia SE</t>
+          <t>Alliance Global Group, Inc</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>26</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>16841</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>ALGGY</t>
+          <t>DWHHF</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Alliance Global Group, Inc</t>
+          <t>Deutsche Wohnen SE</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -9758,100 +9726,100 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>26</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>1140</v>
+        <v>9453</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>DWHHF</t>
+          <t>TIHRF</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Deutsche Wohnen SE</t>
+          <t>Tharisa plc</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>9453</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>TIHRF</t>
+          <t>TPSRF</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Tharisa plc</t>
+          <t>Topsports International Ho</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>471</v>
+        <v>786</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>ANPMF</t>
+          <t>SBHGF</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Andean Precious Metals Cor</t>
+          <t>SBI Holdings, Inc.</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -9860,66 +9828,66 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>664</v>
+        <v>13535</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>TPSRF</t>
+          <t>PTBRY</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Topsports International Ho</t>
+          <t>PT Bank Negara Indonesia (</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>23</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>786</v>
+        <v>7534</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>SBHGF</t>
+          <t>YLLXF</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SBI Holdings, Inc.</t>
+          <t>Yellow Cake plc</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -9928,66 +9896,66 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>13535</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>PTBRY</t>
+          <t>PXGYF</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>PT Bank Negara Indonesia (</t>
+          <t>PAX Global Technology Limi</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>7534</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>YLLXF</t>
+          <t>FPAFY</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Yellow Cake plc</t>
+          <t>First Pacific Company Limi</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>JE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -9996,27 +9964,27 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.89</v>
+        <v>0.6</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>22</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>1879</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>PXGYF</t>
+          <t>FPAFF</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>PAX Global Technology Limi</t>
+          <t>First Pacific Company Limi</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -10026,113 +9994,113 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>22</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>504</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>FPAFY</t>
+          <t>TKGBY</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>First Pacific Company Limi</t>
+          <t>Turkiye Garanti Bankasi A.</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.59</v>
+        <v>1.15</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>2646</v>
+        <v>11130</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>FPAFF</t>
+          <t>FCXXF</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>First Pacific Company Limi</t>
+          <t>First Capital Real Estate</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.59</v>
+        <v>1</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>2680</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKGBY</t>
+          <t>IVSBF</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Turkiye Garanti Bankasi A.</t>
+          <t>Investor AB (publ)</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>1.15</v>
@@ -10141,125 +10109,125 @@
         <v>21</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>11130</v>
+        <v>126624</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>FCXXF</t>
+          <t>IVSXF</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>First Capital Real Estate</t>
+          <t>Investor AB (publ)</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>21</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>3414</v>
+        <v>125727</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>IVSBF</t>
+          <t>ACNDF</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Investor AB (publ)</t>
+          <t>CapitaLand India Trust</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>21</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>126624</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>IVSXF</t>
+          <t>TOIPY</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Investor AB (publ)</t>
+          <t>Thai Oil Public Company Li</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>1.15</v>
+        <v>0.78</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>21</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>125727</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ACNDF</t>
+          <t>FBASF</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>CapitaLand India Trust</t>
+          <t>Fibra UNO</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -10268,32 +10236,32 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>1072</v>
+        <v>6535</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>TOIPY</t>
+          <t>VLVCY</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Thai Oil Public Company Li</t>
+          <t>Volvo Car AB (publ.)</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -10302,32 +10270,32 @@
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.78</v>
+        <v>0.31</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>3987</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>FBASF</t>
+          <t>VLVOF</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Fibra UNO</t>
+          <t>Volvo Car AB (publ.)</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -10336,100 +10304,100 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>20</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>6535</v>
+        <v>5144</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>SAPLF</t>
+          <t>TGOPY</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Sylvania Platinum Limited</t>
+          <t>3i Group plc</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>BM</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>20</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>362</v>
+        <v>17145</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>VLVCY</t>
+          <t>TGOPF</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Volvo Car AB (publ.)</t>
+          <t>3i Group plc</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.31</v>
+        <v>0.87</v>
       </c>
       <c r="G57" s="6" t="n">
         <v>20</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>4818</v>
+        <v>35461</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>VLVOF</t>
+          <t>AYALY</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Volvo Car AB (publ.)</t>
+          <t>Ayala Corporation</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -10441,97 +10409,97 @@
         <v>5.1</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>20</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>5144</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TGOPY</t>
+          <t>ICHHF</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>3i Group plc</t>
+          <t>Ichinen Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>20</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>17145</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>TGOPF</t>
+          <t>PPLFY</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>3i Group plc</t>
+          <t>PT Perusahaan Perkebunan L</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>35461</v>
+        <v>614</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>AYALY</t>
+          <t>CMAKY</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Ayala Corporation</t>
+          <t>China Minsheng Banking Cor</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -10540,66 +10508,66 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.58</v>
+        <v>0.25</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4666</v>
+        <v>20399</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>ICHHF</t>
+          <t>AGMJF</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Ichinen Holdings Co., Ltd.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>205</v>
+        <v>645</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>PPLFY</t>
+          <t>CEBCF</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>PT Perusahaan Perkebunan L</t>
+          <t>China Everbright Bank Comp</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -10608,27 +10576,27 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>19</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>614</v>
+        <v>21041</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>CMAKY</t>
+          <t>CHPXF</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>China Minsheng Banking Cor</t>
+          <t>China Pacific Insurance (G</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -10638,26 +10606,26 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
         <v>5.4</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>19</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>20399</v>
+        <v>38481</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>385 names. CAVEAT: net-net/NCAV figures are in the reporting currency and ADR ratios distort per-share comparisons, so balance-sheet screens are NOT applied here. Usually better executed on the home exchange.</t>
+          <t>386 names. CAVEAT: net-net/NCAV figures are in the reporting currency and ADR ratios distort per-share comparisons, so balance-sheet screens are NOT applied here. Usually better executed on the home exchange.</t>
         </is>
       </c>
     </row>

--- a/OTC_BOOK.xlsx
+++ b/OTC_BOOK.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Going Dark" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="NOL Shells" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Foreign OTC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="OTC Intent" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -638,6 +639,21 @@
       <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Cheap foreign lines on currency-neutral ratios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>OTC Intent</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Management communications signalling buybacks / tenders / capital return.</t>
         </is>
       </c>
     </row>
@@ -656,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -668,6 +684,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -691,6 +708,7 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
@@ -739,6 +757,11 @@
           <t>$vol/day k</t>
         </is>
       </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Mgmt intent</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -776,6 +799,11 @@
       <c r="I5" s="12" t="n">
         <v>7.6</v>
       </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>△ buyback</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -815,6 +843,11 @@
       <c r="I6" s="13" t="n">
         <v>1</v>
       </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -852,6 +885,11 @@
       <c r="I7" s="12" t="n">
         <v>1.4</v>
       </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -889,6 +927,11 @@
       <c r="I8" s="13" t="n">
         <v>1</v>
       </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -926,6 +969,11 @@
       <c r="I9" s="12" t="n">
         <v>14.6</v>
       </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -963,6 +1011,11 @@
       <c r="I10" s="13" t="n">
         <v>2.8</v>
       </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1000,6 +1053,11 @@
       <c r="I11" s="12" t="n">
         <v>2.8</v>
       </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -1037,6 +1095,11 @@
       <c r="I12" s="13" t="n">
         <v>1.6</v>
       </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1074,6 +1137,11 @@
       <c r="I13" s="12" t="n">
         <v>2.1</v>
       </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1113,6 +1181,11 @@
       <c r="I14" s="13" t="n">
         <v>4.3</v>
       </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1150,6 +1223,11 @@
       <c r="I15" s="12" t="n">
         <v>11</v>
       </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1187,6 +1265,11 @@
       <c r="I16" s="13" t="n">
         <v>14.2</v>
       </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1224,6 +1307,11 @@
       <c r="I17" s="12" t="n">
         <v>4.6</v>
       </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1263,6 +1351,11 @@
       <c r="I18" s="13" t="n">
         <v>6.9</v>
       </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1302,6 +1395,11 @@
       <c r="I19" s="12" t="n">
         <v>16</v>
       </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -1339,6 +1437,11 @@
       <c r="I20" s="13" t="n">
         <v>11.6</v>
       </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>buyback</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
@@ -1349,9 +1452,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1363,7 +1466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1375,6 +1478,7 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1398,6 +1502,7 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
@@ -1446,6 +1551,11 @@
           <t>52w pos</t>
         </is>
       </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Mgmt intent</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1481,6 +1591,11 @@
       <c r="I5" s="6" t="n">
         <v>33</v>
       </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -1516,6 +1631,11 @@
       <c r="I6" s="9" t="n">
         <v>28</v>
       </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1551,6 +1671,11 @@
       <c r="I7" s="6" t="n">
         <v>3</v>
       </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -1586,6 +1711,11 @@
       <c r="I8" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1621,6 +1751,11 @@
       <c r="I9" s="6" t="n">
         <v>100</v>
       </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1656,6 +1791,11 @@
       <c r="I10" s="9" t="n">
         <v>93</v>
       </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1691,6 +1831,11 @@
       <c r="I11" s="6" t="n">
         <v>83</v>
       </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -1726,6 +1871,11 @@
       <c r="I12" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>▲ tender 4%</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1761,6 +1911,11 @@
       <c r="I13" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1796,6 +1951,11 @@
       <c r="I14" s="9" t="n">
         <v>77</v>
       </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1831,6 +1991,11 @@
       <c r="I15" s="6" t="n">
         <v>53</v>
       </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1866,6 +2031,11 @@
       <c r="I16" s="9" t="n">
         <v>33</v>
       </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>▲ governance</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1901,6 +2071,11 @@
       <c r="I17" s="6" t="n">
         <v>44</v>
       </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1938,6 +2113,11 @@
       <c r="I18" s="9" t="n">
         <v>36</v>
       </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1973,6 +2153,11 @@
       <c r="I19" s="6" t="n">
         <v>40</v>
       </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -2008,6 +2193,11 @@
       <c r="I20" s="9" t="n">
         <v>41</v>
       </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2043,6 +2233,11 @@
       <c r="I21" s="6" t="n">
         <v>73</v>
       </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>△ buyback</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -2078,6 +2273,11 @@
       <c r="I22" s="9" t="n">
         <v>98</v>
       </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2113,6 +2313,11 @@
       <c r="I23" s="6" t="n">
         <v>56</v>
       </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -2148,6 +2353,11 @@
       <c r="I24" s="9" t="n">
         <v>81</v>
       </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>buyback</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2183,6 +2393,11 @@
       <c r="I25" s="6" t="n">
         <v>57</v>
       </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>▲ buyback 3%</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -2218,6 +2433,11 @@
       <c r="I26" s="9" t="n">
         <v>29</v>
       </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2253,6 +2473,11 @@
       <c r="I27" s="6" t="n">
         <v>85</v>
       </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -2288,6 +2513,11 @@
       <c r="I28" s="9" t="n">
         <v>44</v>
       </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2323,6 +2553,11 @@
       <c r="I29" s="6" t="n">
         <v>84</v>
       </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>△ dividend return</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
@@ -2358,6 +2593,11 @@
       <c r="I30" s="9" t="n">
         <v>91</v>
       </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -2393,6 +2633,11 @@
       <c r="I31" s="6" t="n">
         <v>96</v>
       </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -2428,6 +2673,11 @@
       <c r="I32" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2463,6 +2713,11 @@
       <c r="I33" s="6" t="n">
         <v>3</v>
       </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -2498,6 +2753,11 @@
       <c r="I34" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>strategic review</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -2533,6 +2793,11 @@
       <c r="I35" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
@@ -2568,6 +2833,11 @@
       <c r="I36" s="9" t="n">
         <v>93</v>
       </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -2603,6 +2873,11 @@
       <c r="I37" s="6" t="n">
         <v>38</v>
       </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
@@ -2638,6 +2913,11 @@
       <c r="I38" s="9" t="n">
         <v>97</v>
       </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -2673,6 +2953,11 @@
       <c r="I39" s="6" t="n">
         <v>88</v>
       </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
@@ -2708,6 +2993,11 @@
       <c r="I40" s="9" t="n">
         <v>98</v>
       </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -2743,6 +3033,11 @@
       <c r="I41" s="6" t="n">
         <v>37</v>
       </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>▲ buyback 2%</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
@@ -2778,6 +3073,11 @@
       <c r="I42" s="9" t="n">
         <v>74</v>
       </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -2813,6 +3113,11 @@
       <c r="I43" s="6" t="n">
         <v>66</v>
       </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -2848,6 +3153,11 @@
       <c r="I44" s="9" t="n">
         <v>45</v>
       </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -2883,6 +3193,11 @@
       <c r="I45" s="6" t="n">
         <v>59</v>
       </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
@@ -2918,6 +3233,11 @@
       <c r="I46" s="9" t="n">
         <v>68</v>
       </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2953,6 +3273,11 @@
       <c r="I47" s="6" t="n">
         <v>66</v>
       </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
@@ -2988,6 +3313,11 @@
       <c r="I48" s="9" t="n">
         <v>31</v>
       </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -3023,6 +3353,11 @@
       <c r="I49" s="6" t="n">
         <v>86</v>
       </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
@@ -3058,6 +3393,11 @@
       <c r="I50" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -3093,6 +3433,11 @@
       <c r="I51" s="6" t="n">
         <v>88</v>
       </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
@@ -3128,6 +3473,11 @@
       <c r="I52" s="9" t="n">
         <v>71</v>
       </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -3165,6 +3515,11 @@
       <c r="I53" s="6" t="n">
         <v>23</v>
       </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
@@ -3200,6 +3555,11 @@
       <c r="I54" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
@@ -3210,9 +3570,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3224,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3235,6 +3595,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3257,6 +3618,7 @@
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
@@ -3300,6 +3662,11 @@
           <t>Runway yrs</t>
         </is>
       </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Mgmt intent</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -3334,6 +3701,11 @@
       <c r="H5" s="6" t="n">
         <v>1.7</v>
       </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3370,6 +3742,11 @@
           <t>∞</t>
         </is>
       </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -3406,6 +3783,11 @@
           <t>∞</t>
         </is>
       </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>monetize</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -3440,6 +3822,11 @@
       <c r="H8" s="9" t="n">
         <v>2.7</v>
       </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>strategic review</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -3474,6 +3861,11 @@
       <c r="H9" s="6" t="n">
         <v>1.3</v>
       </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -3508,6 +3900,11 @@
       <c r="H10" s="9" t="n">
         <v>1.1</v>
       </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -3542,6 +3939,11 @@
       <c r="H11" s="6" t="n">
         <v>3.7</v>
       </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -3578,6 +3980,11 @@
           <t>∞</t>
         </is>
       </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -3612,6 +4019,11 @@
       <c r="H13" s="6" t="n">
         <v>18.4</v>
       </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
@@ -3622,9 +4034,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10645,6 +11057,3355 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="64" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OTC Intent — management says it will act (calls, press releases, letters)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Most OTC companies never hold a call, so this reads where they do talk: press releases (full text from the wire), SEC 8-K EX-99 exhibits (results, shareholder letters, buyback/tender notices) and calls where they exist — clause-level commitment, negation, new-vs-routine, and the SIZE of any buyback/tender vs market cap. ● = also on a cheapness screen here.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Mcap $M</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Docs 12m</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Evidence (verbatim, dated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AANNF ●</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Aroundtown S.A.</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2516.2</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>call:3 pr:1</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-26 call] “We continue to execute our share buyback program launched in January, taking advantage of the market volatility and repurchasing our own shares at a significant discount ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MRETF ●</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Martinrea International</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>520.4</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>call:3 pr:9</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-04 call] “As Pat noted, we sold a majority stake in our fluids plant in China during the quarter, further reducing our presence in the region, and we are exploring other potential ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>HKHGF ●</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Hongkong Land Holdings L</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>18137.9</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>call:1</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-29 call] “Since we launched the buyback, we've invested close to $500,000,000.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>KAEPF ●</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>The Kansai Electric Powe</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>21055.7</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>call:1</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>[2026-04-30 call] “For that, we will generate over JPY 380 billion in cash through asset recycling, including the divestment of our shareholdings.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TGONF ●</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Tetragon Financial Group</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1136.2</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>call:1 pr:22</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>[2026-04-14 pr] “Tetragon announces the final results of the "modified Dutch auction" tender offer to purchase a portion of the outstanding non-voting shares of Tetragon for a maximum agg”</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>VXRT ●</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Vaxart, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>call:3 ex99:2 letter:3 pr:23</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>[2025-11-05 pr] “Dynavax Reports Third Quarter 2025 Financial Results and Announces New $100 Million Share Repurchase Program”</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>STGPF ●</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Scentre Group</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>13135.8</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>call:2 pr:3</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>[2026-04-30 pr] “On April 22, 2026, RE1 Limited, in its capacity as responsible entity and trustee of Scentre Group Trust 2 (the "Offeror"), a trust forming part of the stapled entity Sce”</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>GRNNF ●</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Grand City Properties S.</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1810.6</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>call:3 pr:1</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-12 call] “In the second quarter, we issued EUR 600 million of new notes at a coupon of 5.25%, following the transaction we executed in the fourth quarter of last year and completed”</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>OILSF ●</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Saturn Oil &amp; Gas Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>888.1</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>call:2 pr:19</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>[2026-05-07 call] “Since August of 2025, when we renewed our NCIB, the number of shares we have bought back is nearing the maximum allowable for a 1-year period, equal to 12.1 million share”</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>FMCQF ●</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Fresenius Medical Care A</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>11849.1</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>call:4</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-04 call] “After canceling 8.5% of shares, which we bought back as part of the share buyback program completed in April of this year, we initiated a new share buyback program starti”</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>EOHDF ●</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Emeco Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>408.6</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-19 call] “Given the sustained cash generation and strong balance sheet, the board has approved an on-market share buyback of up to 10% of shares on issue.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>GRWXF ●</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Molten Ventures Ord</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>[2026-06-09 call] “We still have about GBP 4 million of the most recent announced buyback tranche left to run.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>NPSNY ●</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Naspers Limited</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>6960.6</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>call:2 pr:1</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>[2026-06-29 call] “On the share buyback — last year we sold about $2 billion from non-core assets, and in the first quarter of this year almost a billion.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>GRGTF ●</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Grainger plc</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>1626.4</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-20 call] “We've done GBP 82 million of sales of our non-core assets and that's either completed or exchanged in the year-to-date.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>NOEJF ●</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>NORMA Group SE</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>call:3</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>[2026-03-31 call] “However, now with the divestment, with the new situation with the new strategy, we will have a good basis for new NORMA, and therefore, we are going to reset and start wi”</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>SPFX ●</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Standard Premium Finance</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>ex99:1 pr:16</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>[2026-04-28 pr] “(OTCQX: SPFX) (“Standard Premium”), a leading specialty finance company, today announces that the Company has repurchased 76,000 shares at $2.25 per share through a board”</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TWODF ●</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Taylor Wimpey plc</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>3612.5</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>[2026-03-05 call] “Accordingly, today, we are announcing a final 2025 dividend of GBP 0.0295 per share, equivalent to GBP 105 million and a GBP 52 million share buyback, which will commence”</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>KRNGF ●</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Karoon Energy Ltd</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>845.7</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-26 call] “Since the 30th of June, we have completed a further USD 15 million buyback tranche, purchasing approximately 12.6 million shares between the 23rd of July and the 7th of A”</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>PAFRY ●</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Pan African Resources PL</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>[2026-09-16 call] “The Board has also approved a share buyback program to purchase up to ZAR 500 million or approximately $30 million of ordinary shares of the company, commencing during Oc”</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>IPXHF ●</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Inpex Corporation</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>30170.4</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-07 call] “From that standpoint, we think internally, we think we are undervalued and that is, as a company, the understanding we have today.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>ONEXF ●</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Onex Corporation</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>5886.7</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>call:3 pr:14</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-13 call] “Our strategy will include both share repurchases and deploying capital into 1 or 2 additional investments that can deliver compelling risk-adjusted returns for shareholde”</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>MSADF ●</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>MS&amp;AD Insurance Group Ho</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>46328.5</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-20 call] “In addition to this, we plan to repurchase JPY 80 billion of our own shares during the first half as part of our basic shareholder return and combined with JPY 190 billio”</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TIHRF ●</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Tharisa plc</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>471.1</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>[2026-05-21 call] “Profit before tax, also strongly up at $69.9 million, translating to earnings per share of $0.158 per share, that's up 532% -- and very pleasing, the Board approved an in”</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>LIMAF ●</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Linamar Corporation</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>4057.3</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>call:3 pr:11</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>[2025-10-09 pr] “(“Aludyne” or the “Company”), a global lightweighting solutions and components supplier to the mobility industry, today announced that it has entered into a definitive ag”</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>CDEVY ●</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>City Developments Limite</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>5315.7</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>call:1</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-12 call] “But anyway, all that we will share more when we release our strategic review outcome end of next month.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>IMPJY ●</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Webuild S.p.A.</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>2305.1</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>call:1</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>[2026-07-30 call] “And in line with the direction of that plan, yesterday, we announced to launch a voluntary tender offer for all the ordinary share of Trevi.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>FRFFF ●</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Fairfax Financial Holdin</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>15669.4</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>call:4 pr:6</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-31 call] “So we think it still remains undervalued.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>HDIUF ●</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>ADENTRA Inc.</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>642.3</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-06 call] “During the quarter, we returned approximately $5.6 million to shareholders through dividends and share repurchases.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>PARXF ●</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Parex Resources Inc.</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>1824.5</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>call:4 pr:11</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-31 call] “This focus will drive compounding efficiencies and expand our free cash flow profile, giving us the flexibility to reinvest in organic growth, strengthen our balance shee”</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>NHOLF ●</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Sompo Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>39116</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-20 call] “As to share buyback, we have decided to buy back shares worth JPY 69 billion for the second half, making the total annual amount JPY 146 billion.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>CKHUF ●</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>CK Hutchison Holdings Li</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>32517.1</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-13 call] “And as a result, they increased their dividend by close to 3% to HKD 0.75, right, marking, I think, the 30th year in a row that we managed to grow and grow dividends in t”</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>VGPBF ●</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Vgp N.V.</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>2488.5</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>call:2 pr:3</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-20 call] “And also, we bought back EUR 100 million on the January '27 bond outstanding.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SUMXF ●</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Supremex Inc.</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>call:3 pr:8</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>[2025-11-06 call] “In this regard, following the launch of a normal course issuer bid program in August, we repurchased approximately 44,000 shares in Q3 for a consideration of $0.2 million”</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>NNGPF ●</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>NN Group N.V.</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>23839</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-06 call] “And we remain firmly committed to extending that track record with total capital return to shareholders foreseen to grow over EUR 15 billion by 2028 based on current comm”</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>ETST ●</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Earth Science Tech, Inc.</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>ex99:9 letter:1 pr:17</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>[2026-06-18 ex99] “During fiscal 2026 and subsequent to year end, we repurchased and retired more than 7.1 million shares of common stock, continued investing in new products and expanded t”</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>CMRB</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>First Commerce Bank</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>pr:10</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>[2026-03-30 pr] “President &amp; CEO Donald Mindiak commented, "On the heels of a capital raise in the form of a $40.0 million Subordinated Debt Offering, which was noteworthy in that it was ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>AIMFF</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Aimia Inc.</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>call:4</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-11 call] “We completed a tender offer to purchase senior notes due in January 2030, reducing our interest costs materially.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>WNDLF</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Wendel</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>3549.5</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>call:2 pr:17</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>[2026-02-26 call] “The sale of Stahl is going to bring $1.2 billion of net proceeds to Wendel and the expected tender offer on IHS should bring $575 million for the shares that we own in IH”</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>LNWO</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Light &amp; Wonder, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>6215.1</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>call:3 ex99:5 pr:7</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-04 call] “Since the inception of our first ever share repurchase program back in 2022, we have returned $2.1 billion to shareholders.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>CURLF</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Curaleaf Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>3094.2</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>call:3 pr:66</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>[2026-04-16 pr] “(TSX: CURA) (OTCQX: CURLF ) ("Curaleaf" or the "Company"), a leading international provider of consumer cannabis products, has announced that its Board of Directors has a”</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>CSHX</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Cashmere Valley Bank</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>333.1</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>pr:13</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>[2026-03-18 pr] “Cashmere Valley Bank Commences Self Tender Offer to Repurchase up to 200,000 Shares of its Common Stock”</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>PRPH</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>ProPhase Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>call:1 pr:14</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>[2025-11-19 call] “Then the Crown Medical, $20 million is going to come in, and I am going to buy back half the shares outstanding in the company.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>LOQPF</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>accesso Technology Group</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>call:2 pr:1</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>[2026-03-30 call] “And then on the 18th of March, we completed a tender offer that you will all have seen for $20 million returning or purchasing and canceling 4.8 million shares and just s”</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>BTDPY</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Barratt Redrow PLC Unspo</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>2790.7</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>[2026-09-16 call] “Over the last 10 years, we have returned nearly GBP 3.5 billion to shareholders, with GBP 1 billion returned through share buyback or special dividends.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>CLILF</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>CapitaLand Investment Li</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>10225.1</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-12 call] “Private funds contribution has increased, is expected to also increase going forward as we've been divesting some of our lower-yielding assets and reinvesting into credit”</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>VREOF</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Vireo Growth Inc.</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>call:2 ex99:10 pr:32</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-18 ex99] “("Vireo" or the "Company") (CSE: VREO; OTCQX: VREOF), a leading vertically integrated cannabis company and agricultural markets platform, today announced it has received ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>EXXRF</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Exor N.V.</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>16714.5</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>call:2 pr:9</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>[2026-09-23 call] “You'll see also in the announcement that we are very explicit that both because the shares trade at a substantial discount to our NAV and don't reflect our assessment of ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>SGBAF</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Ses S.a.</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>2311.8</v>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>call:4 pr:100</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>[2026-07-31 pr] “In the time period from June 2, 2026 until and including June 23, 2026, a number of 213,167 shares were bought back within the framework of the share buyback of SES to me”</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>EUZOF</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Eurazeo SE</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>2936.7</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-23 call] “In 2026, we have already distributed a dividend per share increasing by 10% and executed half of the share buyback program for the year.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>MUEL</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Paul Mueller Company</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>594.3</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>pr:13</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-07 pr] “Paul Mueller Company (OTC: MUEL) (the “Company”) today announced that the Board of Directors has approved a tender offer (the “Tender Offer”) to repurchase up to 35,000 s”</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>UTGPF</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Unite Group Plc</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>3437.4</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>call:2 pr:23</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-28 call] “We've completed GBP 165 million of share buybacks in H1, and we still see Unite shares as the best way for us to invest in high-quality student accommodation today.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>LTUM</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Lithium Corporation</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>pr:100</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>[2026-09-10 pr] “To exercise the Option and acquire a 100% interest in the Property, Osisko must: (a) make the following cash payments to the Company: (i) $100,000 on the Effective Date; ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>APNHY</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Aspen Pharmacare Holding</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>4462.4</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>[2026-09-03 call] “And as we said, we -- I think as at 2 days ago, we announced a 3% share buyback at ZAR 2 billion of investment.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>RHEPB</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Regional Health Properti</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>ex99:3</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>[2025-12-01 ex99] “(the “Company”, “Regional”, “we”, “us” or “our”) (OTCQB: RHEP) (OTCQB: RHEPA) (OTCQB: RHEPB) (OTCQB:RHEPZ), today announced that its Board of Directors authorized and app”</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>BTRCF</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Better Collective A/S</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>881.1</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>call:4</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>[2026-05-21 call] “In March, we launched a new share buyback program of up to EUR 40 million.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>GTBIF</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Green Thumb Industries I</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>1677.5</v>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>call:1 ex99:5 pr:17</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-06 ex99] “• Repurchased approximately 7.4 million additional Subordinate Voting Shares, bringing 2026 year-to-date repurchases to approximately 13.4 million Subordinate Voting Shar”</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>ZSPC</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>zSpace, Inc.</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>call:3 ex99:7 pr:100</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>[2026-05-14 ex99] “Board of Directors Launches Strategic Alternatives Review to Unlock Shareholder Value”</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>FBBPF</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>FIBRA Prologis</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>7256.7</v>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>call:4 pr:23</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>[2026-04-30 call] “We will eventually sell our non-core portfolio.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>OTCM</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>OTC Markets Group Inc.</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>662.2</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>call:3 pr:87</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>[2026-03-05 call] “During 2025, we returned a total of $32,600,000 to investors in the form of dividends and through our stock buyback program, a 10% increase from the prior year primarily ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>VTMTF</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Vertu Motors plc</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>360</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-18 call] “And to date, we have in the form of dividends and buybacks, returned GBP 112 million in cash, reflecting the strong underlying cash flows of the group.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>ALYAF</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Alithya Group Inc.</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>call:3 pr:12</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>[2026-02-13 call] “In connection with the Datum transaction that Paul alluded to earlier, we will be repurchasing close to 2.5 million Class A shares from Amar.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>CCFN</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Muncy Columbia Financial</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>ex99:8 letter:1 pr:9</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>[2026-05-12 ex99] “The program authorizes the repurchase of up to an additional 530,611 shares, or 5% of the Corporation's issued and outstanding common shares as of May 15, 2026.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>VSTKF</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>VNV Global AB (publ)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>252.2</v>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>call:4</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>[2026-04-22 call] “Also sort of during the quarter, we bought back another close to 500,000 VNV shares and also a small amount of the outstanding bonds, which I'll come to now, which we als”</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>BKSC</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Bank of South Carolina C</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>pr:9</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>[2025-12-18 pr] “This new repurchase program replaces the previous stock repurchase program approved by the Board on May 25, 2023, which recently concluded with the successful repurchase ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>DEXSF</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Dexus</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>4105.3</v>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-20 call] “So, I think we see opportunity to sell assets where kind of the go-forward returns are going to not meet our hurdles or returns relative to the redeployment opportunities”</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>ENTOF</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Entra ASA</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>2034.8</v>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>call:3</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>[2026-04-21 call] “Divestments of negative NOK 553 million is related to the Christian Krohgs gate 2 project or joint venture project we have with Skanska, which we announced in the fourth ”</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>GLXZ</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Galaxy Gaming, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>ex99:6 pr:9</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-22 ex99] “GALAXY GAMING BOARD AUTHORIZES $4 MILLION SHARE REPURCHASE PROGRAM”</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>PRTCY</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>PureTech Health plc</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>call:2 pr:1</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>[2026-09-22 call] “In practice, this means that we will prioritize maintaining an appropriate operational runway, selectively deploying capital where we see compelling risk-adjusted opportu”</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>SMBMF</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Seatrium Limited</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>5286.4</v>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-30 call] “Upon completion, we intend to launch a new share buyback program to enhance shareholder value.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>ONEI</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>OneMeta AI</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>ex99:1 pr:13</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>[2026-04-14 pr] “The Company repurchased 4,166,667 shares of its Series B-1 Preferred Stock for an aggregate purchase price of $2,750,000.22.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>CCGPY</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>C&amp;C Group plc</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>540.4</v>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>[2025-10-27 call] “Clearly, our preference is for the former, and we completed the latest EUR 15 million tranche of share buybacks in September of this year.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>RIOCF</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>RioCan Real Estate Inves</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G76" s="13" t="n">
+        <v>4275</v>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>call:3 pr:28</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-04 call] “This extends beyond operations to capital allocation, where we've made significant progress, including the near completion of the RioCan Living portfolio monetization.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>MBAK</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>MBAK Energy Solutions In</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>pr:9</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>[2026-02-03 pr] “(OTC:MBAK) Announces $500,000 Share Repurchase Plan”</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>AAWH</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Ascend Wellness Holdings</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>call:3 ex99:1 pr:18</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>[2025-11-10 call] “Since the launch of the buyback initiative last year, we have repurchased and retired approximately 5 million shares at an average price of $0.30 per share.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>LLESF</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Lendlease Group</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>1354.1</v>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>call:2</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>[2026-08-19 call] “We're looking to take costs out of that ahead of asset sales, and then that will wind down with asset sales.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>HUSQF</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Husqvarna AB</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>2356.1</v>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>call:4 pr:1</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>[2026-07-17 call] “Today, we also announced that we will move from a turnaround case to a strategic review of our Powered Garden business portfolio unit within the Gardena division.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>CIBH</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>CIB Marine Bancshares, I</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>pr:7</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>[2026-05-01 pr] “As a result, the total amount authorized for the repurchase of the Company's outstanding common stock has increased from $2.5 million to $3.5 million with the program con”</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>CVAT</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Cavitation Technologies,</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>ex99:1 pr:13</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>[2026-08-19 ex99] “(OTCQB: CVAT) ("CVAT" or the "Company"), a leading provider of sustainable nanotechnology solutions, today announced that, on August 14, 2026, the Company executed a defi”</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>SCBFF</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Standard Chartered PLC</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>65112.2</v>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>call:3 pr:9</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>[2026-07-29 call] “And even after today, we'll still be very happy to buy back $1 billion of shares at this price.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>AAVVF</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Advantage Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>ACT SIGNALLED</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>1197.9</v>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>call:3</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>[2026-07-31 call] “Share buybacks are going to be our main vehicle for shareholder returns while our shares are trading below intrinsic value.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>244 OTC names with a current intent signal (ACT SIGNALLED = top decile with a realised/committed shareholder action, a NEW family vs the prior 12 months, or a stated buyback/tender &gt;= 5% of mcap; BUILDING = top quartile; last document &lt;= 200 days old). Weights come from the earnings-call validation (tender 2.2x, buyback/dividend 1.6x, value-gap 1.4x lift for subsequent action). Language predicts ACTION, not the re-rating by itself — pair it with the cheapness tabs. See OTC_INTENT_VALIDATION.md. Source: otc_comms.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A86:I86"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/OTC_BOOK.xlsx
+++ b/OTC_BOOK.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>P/B 0.26 · 26.4× EBITDA · debt 704% · 52w 6%</t>
+          <t>P/B 0.26 · 26.4× EBITDA · debt 705% · 52w 6%</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 704% of mcap · rev +14% · op margin 60%  [share-count history inconsistent (foreign line)]</t>
+          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 705% of mcap · rev +14% · op margin 60%  [share-count history inconsistent (foreign line)]</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 704% of mcap · rev +14% · op margin 60%  [share-count history inconsistent (foreign line)]</t>
+          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 705% of mcap · rev +14% · op margin 60%  [share-count history inconsistent (foreign line)]</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>-704%</t>
+          <t>-705%</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>-704%</t>
+          <t>-705%</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 704% of mcap · rev +14% · op margin 60%</t>
+          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 705% of mcap · rev +14% · op margin 60%</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="I191" s="13" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-49%</t>
         </is>
       </c>
       <c r="J191" s="13" t="n">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="R191" s="13" t="inlineStr">
         <is>
-          <t>P/B 4.84 · EV/EBITDA 3.4× · FCF yld 79% · net debt 50% of mcap · rev +11% · op margin 11%</t>
+          <t>P/B 4.84 · EV/EBITDA 3.4× · FCF yld 79% · net debt 49% of mcap · rev +11% · op margin 11%</t>
         </is>
       </c>
       <c r="S191" s="13" t="inlineStr">
@@ -28863,7 +28863,7 @@
       </c>
       <c r="I196" s="14" t="inlineStr">
         <is>
-          <t>-256%</t>
+          <t>-257%</t>
         </is>
       </c>
       <c r="J196" s="14" t="n">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="R196" s="14" t="inlineStr">
         <is>
-          <t>P/B 0.41 · EV/EBITDA 11.2× · FCF yld 13% · net debt 256% of mcap · rev +4% · op margin 35%</t>
+          <t>P/B 0.41 · EV/EBITDA 11.2× · FCF yld 13% · net debt 257% of mcap · rev +4% · op margin 35%</t>
         </is>
       </c>
       <c r="S196" s="14" t="inlineStr"/>
@@ -37159,8 +37159,10 @@
       <c r="D297" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="E297" s="13" t="n">
-        <v>179.55</v>
+      <c r="E297" s="13" t="inlineStr">
+        <is>
+          <t>n/m</t>
+        </is>
       </c>
       <c r="F297" s="13" t="inlineStr">
         <is>
@@ -47541,7 +47543,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>P/B 4.84 · 3.4× EBITDA · debt 50% · 52w 100%</t>
+          <t>P/B 4.84 · 3.4× EBITDA · debt 49% · 52w 100%</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -47568,7 +47570,7 @@
       </c>
       <c r="J10" s="26" t="inlineStr">
         <is>
-          <t>P/B 4.84 · EV/EBITDA 3.4× · FCF yld 79% · net debt 50% of mcap · rev +11% · op margin 11%  [dividend yield &gt;25% (special or bad data)]</t>
+          <t>P/B 4.84 · EV/EBITDA 3.4× · FCF yld 79% · net debt 49% of mcap · rev +11% · op margin 11%  [dividend yield &gt;25% (special or bad data)]</t>
         </is>
       </c>
     </row>
@@ -47761,7 +47763,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>P/B 0.41 · 11.2× EBITDA · debt 256% · 52w 33%</t>
+          <t>P/B 0.41 · 11.2× EBITDA · debt 257% · 52w 33%</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -47788,7 +47790,7 @@
       </c>
       <c r="J15" s="25" t="inlineStr">
         <is>
-          <t>P/B 0.41 · EV/EBITDA 11.2× · FCF yld 13% · net debt 256% of mcap · rev +4% · op margin 35%</t>
+          <t>P/B 0.41 · EV/EBITDA 11.2× · FCF yld 13% · net debt 257% of mcap · rev +4% · op margin 35%</t>
         </is>
       </c>
     </row>
@@ -48113,7 +48115,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>P/B 0.26 · 26.4× EBITDA · debt 704% · 52w 6%</t>
+          <t>P/B 0.26 · 26.4× EBITDA · debt 705% · 52w 6%</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -48140,7 +48142,7 @@
       </c>
       <c r="J23" s="25" t="inlineStr">
         <is>
-          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 704% of mcap · rev +14% · op margin 60%  [share-count history inconsistent (foreign line)]</t>
+          <t>P/B 0.26 · EV/EBITDA 26.4× · FCF yld 34% · net debt 705% of mcap · rev +14% · op margin 60%  [share-count history inconsistent (foreign line)]</t>
         </is>
       </c>
     </row>
